--- a/dados/royalties_rj.xlsx
+++ b/dados/royalties_rj.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antonio.azevedo.SAD_PMN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacqu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F838BD-5439-4B34-B0F0-C2850AE81736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36346307-A212-4C26-AA16-94A6B82C0DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="18270" windowHeight="11550" tabRatio="659" xr2:uid="{EE56A0C3-3F76-41D8-BD97-D27B975C9833}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="659" xr2:uid="{EE56A0C3-3F76-41D8-BD97-D27B975C9833}"/>
   </bookViews>
   <sheets>
     <sheet name="Royalties RJ" sheetId="15" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>ANGRA DOS REIS-RJ</t>
   </si>
@@ -631,6 +631,12 @@
   </si>
   <si>
     <t>Código MU</t>
+  </si>
+  <si>
+    <t>TOTAL 2022</t>
+  </si>
+  <si>
+    <t>TOTAL 2023</t>
   </si>
 </sst>
 </file>
@@ -696,7 +702,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -719,14 +725,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -737,11 +759,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Moeda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 5 2" xfId="1" xr:uid="{B67B9E32-C7E8-4467-973A-C355BA328600}"/>
+    <cellStyle name="Vírgula" xfId="4" builtinId="3"/>
     <cellStyle name="Vírgula 2" xfId="2" xr:uid="{D3DC72BA-27B4-4FED-9E83-06D6B25902EC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -768,9 +792,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -808,7 +832,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -914,7 +938,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,7 +1080,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1064,16 +1088,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53912C20-76DB-4664-B175-29C0B70AC974}">
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>196</v>
       </c>
@@ -1113,8 +1138,14 @@
       <c r="M1" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>104</v>
       </c>
@@ -1154,8 +1185,14 @@
       <c r="M2" s="7">
         <v>188700860.25999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="8">
+        <v>272535712.48000002</v>
+      </c>
+      <c r="O2">
+        <v>240781531.32999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>105</v>
       </c>
@@ -1195,8 +1232,14 @@
       <c r="M3" s="7">
         <v>13878208.789999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="8">
+        <v>20506078.600000001</v>
+      </c>
+      <c r="O3">
+        <v>18587566.779999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>106</v>
       </c>
@@ -1236,8 +1279,14 @@
       <c r="M4" s="7">
         <v>137046629.35000002</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="8">
+        <v>290914554.57999998</v>
+      </c>
+      <c r="O4">
+        <v>427700028.36000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>107</v>
       </c>
@@ -1277,8 +1326,14 @@
       <c r="M5" s="7">
         <v>13878208.789999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="8">
+        <v>34857643.430000007</v>
+      </c>
+      <c r="O5">
+        <v>35811428.640000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>108</v>
       </c>
@@ -1318,8 +1373,14 @@
       <c r="M6" s="7">
         <v>231234949.88</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="8">
+        <v>214932465.21000001</v>
+      </c>
+      <c r="O6">
+        <v>147634730.18000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>109</v>
       </c>
@@ -1359,8 +1420,14 @@
       <c r="M7" s="7">
         <v>151921108.30999997</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="8">
+        <v>278038408.35999995</v>
+      </c>
+      <c r="O7">
+        <v>419067124.27999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>110</v>
       </c>
@@ -1400,8 +1467,14 @@
       <c r="M8" s="7">
         <v>33071564.049999997</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="8">
+        <v>45731795.460000001</v>
+      </c>
+      <c r="O8">
+        <v>40136191.730000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>111</v>
       </c>
@@ -1441,8 +1514,14 @@
       <c r="M9" s="7">
         <v>27044670.710000005</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="8">
+        <v>43138062.900000006</v>
+      </c>
+      <c r="O9">
+        <v>40895384.120000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>112</v>
       </c>
@@ -1482,8 +1561,14 @@
       <c r="M10" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O10">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>113</v>
       </c>
@@ -1523,8 +1608,14 @@
       <c r="M11" s="7">
         <v>17843411.329999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="8">
+        <v>26364958.16</v>
+      </c>
+      <c r="O11">
+        <v>23898066.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>114</v>
       </c>
@@ -1564,8 +1655,14 @@
       <c r="M12" s="7">
         <v>19165145.559999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="8">
+        <v>28317918.080000002</v>
+      </c>
+      <c r="O12">
+        <v>25668293.180000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>115</v>
       </c>
@@ -1605,8 +1702,14 @@
       <c r="M13" s="7">
         <v>283923678.67000002</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="8">
+        <v>307611902.07999998</v>
+      </c>
+      <c r="O13">
+        <v>339275941.55000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>116</v>
       </c>
@@ -1646,8 +1749,14 @@
       <c r="M14" s="7">
         <v>61441719.169999994</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14" s="8">
+        <v>171398836.04000002</v>
+      </c>
+      <c r="O14">
+        <v>153780585.52000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>117</v>
       </c>
@@ -1687,8 +1796,14 @@
       <c r="M15" s="7">
         <v>15199942.959999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15" s="8">
+        <v>22459038.430000003</v>
+      </c>
+      <c r="O15">
+        <v>20357611.780000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>118</v>
       </c>
@@ -1728,8 +1843,14 @@
       <c r="M16" s="7">
         <v>458092083.28000003</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16" s="8">
+        <v>863228543.74999988</v>
+      </c>
+      <c r="O16">
+        <v>697700070.87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>119</v>
       </c>
@@ -1769,8 +1890,14 @@
       <c r="M17" s="7">
         <v>16521677.169999996</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17" s="8">
+        <v>24411998.340000004</v>
+      </c>
+      <c r="O17">
+        <v>22127838.949999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -1810,8 +1937,14 @@
       <c r="M18" s="7">
         <v>70159414.180000007</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18" s="8">
+        <v>101309011.36</v>
+      </c>
+      <c r="O18">
+        <v>105529096.67999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>121</v>
       </c>
@@ -1851,8 +1984,14 @@
       <c r="M19" s="7">
         <v>14539075.819999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19" s="8">
+        <v>21482558.5</v>
+      </c>
+      <c r="O19">
+        <v>19472498.32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>122</v>
       </c>
@@ -1892,8 +2031,14 @@
       <c r="M20" s="7">
         <v>15860810.049999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="8">
+        <v>23435518.359999999</v>
+      </c>
+      <c r="O20">
+        <v>21242725.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>123</v>
       </c>
@@ -1933,8 +2078,14 @@
       <c r="M21" s="7">
         <v>105158332.83</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="8">
+        <v>256987821.68000001</v>
+      </c>
+      <c r="O21">
+        <v>239429657.99000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>124</v>
       </c>
@@ -1974,8 +2125,14 @@
       <c r="M22" s="7">
         <v>13235070.399999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="8">
+        <v>20277984.120000001</v>
+      </c>
+      <c r="O22">
+        <v>18601417.84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>125</v>
       </c>
@@ -2015,8 +2172,14 @@
       <c r="M23" s="7">
         <v>17182544.27</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N23" s="8">
+        <v>25388478.240000002</v>
+      </c>
+      <c r="O23">
+        <v>23012952.470000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>126</v>
       </c>
@@ -2056,8 +2219,14 @@
       <c r="M24" s="7">
         <v>17182544.27</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="8">
+        <v>25388478.240000002</v>
+      </c>
+      <c r="O24">
+        <v>23012952.470000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>127</v>
       </c>
@@ -2097,8 +2266,14 @@
       <c r="M25" s="7">
         <v>13878208.789999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N25" s="8">
+        <v>20506078.600000001</v>
+      </c>
+      <c r="O25">
+        <v>18587384.719999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>128</v>
       </c>
@@ -2138,8 +2313,14 @@
       <c r="M26" s="7">
         <v>124018033.39999998</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="8">
+        <v>191198801.00999999</v>
+      </c>
+      <c r="O26">
+        <v>171184563.35000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>129</v>
       </c>
@@ -2179,8 +2360,14 @@
       <c r="M27" s="7">
         <v>14539075.819999998</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N27" s="8">
+        <v>21482558.5</v>
+      </c>
+      <c r="O27">
+        <v>19472498.32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>130</v>
       </c>
@@ -2220,8 +2407,14 @@
       <c r="M28" s="7">
         <v>69167297.980000004</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N28" s="8">
+        <v>182828807.59</v>
+      </c>
+      <c r="O28">
+        <v>167859070.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>131</v>
       </c>
@@ -2261,8 +2454,14 @@
       <c r="M29" s="7">
         <v>79119135.649999991</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N29" s="8">
+        <v>187721352.82000002</v>
+      </c>
+      <c r="O29">
+        <v>172804954.94999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>132</v>
       </c>
@@ -2302,8 +2501,14 @@
       <c r="M30" s="7">
         <v>31324538.110000003</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N30" s="8">
+        <v>45706476.760000005</v>
+      </c>
+      <c r="O30">
+        <v>41050719.300000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>133</v>
       </c>
@@ -2343,8 +2548,14 @@
       <c r="M31" s="7">
         <v>105902370.31</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N31" s="8">
+        <v>156521992.83999997</v>
+      </c>
+      <c r="O31">
+        <v>140014170.29999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>134</v>
       </c>
@@ -2384,8 +2595,14 @@
       <c r="M32" s="7">
         <v>15199942.959999999</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N32" s="8">
+        <v>22459038.430000003</v>
+      </c>
+      <c r="O32">
+        <v>20357611.780000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>135</v>
       </c>
@@ -2425,8 +2642,14 @@
       <c r="M33" s="7">
         <v>17182544.27</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N33" s="8">
+        <v>25388478.240000002</v>
+      </c>
+      <c r="O33">
+        <v>23012952.470000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>136</v>
       </c>
@@ -2466,8 +2689,14 @@
       <c r="M34" s="7">
         <v>23791215.239999998</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N34" s="8">
+        <v>35153277.729999997</v>
+      </c>
+      <c r="O34">
+        <v>31864088.210000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>137</v>
       </c>
@@ -2507,8 +2736,14 @@
       <c r="M35" s="7">
         <v>18504278.440000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N35" s="8">
+        <v>27341438.229999997</v>
+      </c>
+      <c r="O35">
+        <v>24783179.660000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>138</v>
       </c>
@@ -2548,8 +2783,14 @@
       <c r="M36" s="7">
         <v>32234054.960000005</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N36" s="8">
+        <v>47628998.039999999</v>
+      </c>
+      <c r="O36">
+        <v>41195552.630000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>139</v>
       </c>
@@ -2589,8 +2830,14 @@
       <c r="M37" s="7">
         <v>13217341.68</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N37" s="8">
+        <v>19529598.609999999</v>
+      </c>
+      <c r="O37">
+        <v>17702271.050000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>140</v>
       </c>
@@ -2630,8 +2877,14 @@
       <c r="M38" s="7">
         <v>955218110.90999985</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N38" s="8">
+        <v>1436889507.8499999</v>
+      </c>
+      <c r="O38">
+        <v>1298067220.2699997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>141</v>
       </c>
@@ -2671,8 +2924,14 @@
       <c r="M39" s="7">
         <v>13217341.68</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N39" s="8">
+        <v>19529598.609999999</v>
+      </c>
+      <c r="O39">
+        <v>17702271.050000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>142</v>
       </c>
@@ -2712,8 +2971,14 @@
       <c r="M40" s="7">
         <v>75931842.299999997</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N40" s="8">
+        <v>208486738.25999999</v>
+      </c>
+      <c r="O40">
+        <v>183454978.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>143</v>
       </c>
@@ -2753,8 +3018,14 @@
       <c r="M41" s="7">
         <v>71743866.170000002</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N41" s="8">
+        <v>106834245.71000001</v>
+      </c>
+      <c r="O41">
+        <v>156973930.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>144</v>
       </c>
@@ -2794,8 +3065,14 @@
       <c r="M42" s="7">
         <v>1335294650.6800001</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N42" s="8">
+        <v>2513632772.2599998</v>
+      </c>
+      <c r="O42">
+        <v>2408774084.0700002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>145</v>
       </c>
@@ -2835,8 +3112,14 @@
       <c r="M43" s="7">
         <v>15860810.049999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N43" s="8">
+        <v>23435518.359999999</v>
+      </c>
+      <c r="O43">
+        <v>21242725.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>146</v>
       </c>
@@ -2876,8 +3159,14 @@
       <c r="M44" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N44" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O44">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>147</v>
       </c>
@@ -2917,8 +3206,14 @@
       <c r="M45" s="7">
         <v>54168137.310000002</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N45" s="8">
+        <v>37762163.509999998</v>
+      </c>
+      <c r="O45">
+        <v>23898066.02</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>148</v>
       </c>
@@ -2958,8 +3253,14 @@
       <c r="M46" s="7">
         <v>17843411.329999998</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N46" s="8">
+        <v>26364958.16</v>
+      </c>
+      <c r="O46">
+        <v>23898066.02</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>149</v>
       </c>
@@ -2999,8 +3300,14 @@
       <c r="M47" s="7">
         <v>15199942.959999999</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N47" s="8">
+        <v>22459038.430000003</v>
+      </c>
+      <c r="O47">
+        <v>20357611.780000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>150</v>
       </c>
@@ -3040,8 +3347,14 @@
       <c r="M48" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N48" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O48">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>151</v>
       </c>
@@ -3081,8 +3394,14 @@
       <c r="M49" s="7">
         <v>745280656.52999997</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N49" s="8">
+        <v>1094486347.0900002</v>
+      </c>
+      <c r="O49">
+        <v>962401773.77999997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>152</v>
       </c>
@@ -3122,8 +3441,14 @@
       <c r="M50" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N50" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O50">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>153</v>
       </c>
@@ -3163,8 +3488,14 @@
       <c r="M51" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O51">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>154</v>
       </c>
@@ -3204,8 +3535,14 @@
       <c r="M52" s="7">
         <v>29217935.450000003</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N52" s="8">
+        <v>40010274.490000002</v>
+      </c>
+      <c r="O52">
+        <v>34824720.089999996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>155</v>
       </c>
@@ -3245,8 +3582,14 @@
       <c r="M53" s="7">
         <v>20486879.740000002</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N53" s="8">
+        <v>51456521.420000002</v>
+      </c>
+      <c r="O53">
+        <v>52864490.050000004</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>156</v>
       </c>
@@ -3286,8 +3629,14 @@
       <c r="M54" s="7">
         <v>142181230.68000001</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N54" s="8">
+        <v>178923974.98999998</v>
+      </c>
+      <c r="O54">
+        <v>197856699.64000005</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>157</v>
       </c>
@@ -3327,8 +3676,14 @@
       <c r="M55" s="7">
         <v>56295735.840000011</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N55" s="8">
+        <v>48720350.819999993</v>
+      </c>
+      <c r="O55">
+        <v>31874296.790000007</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>158</v>
       </c>
@@ -3368,8 +3723,14 @@
       <c r="M56" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N56" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O56">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>159</v>
       </c>
@@ -3409,8 +3770,14 @@
       <c r="M57" s="7">
         <v>21509382.289999999</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N57" s="8">
+        <v>36850700.230000004</v>
+      </c>
+      <c r="O57">
+        <v>31309966</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>160</v>
       </c>
@@ -3450,8 +3817,14 @@
       <c r="M58" s="7">
         <v>18174611.399999999</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N58" s="8">
+        <v>29925015.440000001</v>
+      </c>
+      <c r="O58">
+        <v>28742497.57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>161</v>
       </c>
@@ -3491,8 +3864,14 @@
       <c r="M59" s="7">
         <v>15860810.049999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N59" s="8">
+        <v>23435518.359999999</v>
+      </c>
+      <c r="O59">
+        <v>21242725.27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>162</v>
       </c>
@@ -3532,8 +3911,14 @@
       <c r="M60" s="7">
         <v>15860810.049999999</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N60" s="8">
+        <v>25469018.220000003</v>
+      </c>
+      <c r="O60">
+        <v>27255804.770000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>163</v>
       </c>
@@ -3573,8 +3958,14 @@
       <c r="M61" s="7">
         <v>14539075.819999998</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N61" s="8">
+        <v>21482558.5</v>
+      </c>
+      <c r="O61">
+        <v>19472498.32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>164</v>
       </c>
@@ -3614,8 +4005,14 @@
       <c r="M62" s="7">
         <v>25773816.530000001</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N62" s="8">
+        <v>38082717.500000007</v>
+      </c>
+      <c r="O62">
+        <v>34519428.849999994</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>165</v>
       </c>
@@ -3655,8 +4052,14 @@
       <c r="M63" s="7">
         <v>219398818.13999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N63" s="8">
+        <v>269923025.73000002</v>
+      </c>
+      <c r="O63">
+        <v>216960737.94999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>166</v>
       </c>
@@ -3696,8 +4099,14 @@
       <c r="M64" s="7">
         <v>26106296.519999996</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N64" s="8">
+        <v>41332914.730000004</v>
+      </c>
+      <c r="O64">
+        <v>39612169.280000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>167</v>
       </c>
@@ -3737,8 +4146,14 @@
       <c r="M65" s="7">
         <v>21147746.809999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N65" s="8">
+        <v>31247357.960000001</v>
+      </c>
+      <c r="O65">
+        <v>28323633.939999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>168</v>
       </c>
@@ -3778,8 +4193,14 @@
       <c r="M66" s="7">
         <v>15860810.049999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N66" s="8">
+        <v>63961333.709999993</v>
+      </c>
+      <c r="O66">
+        <v>55490058.969999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>169</v>
       </c>
@@ -3819,8 +4240,14 @@
       <c r="M67" s="7">
         <v>47462571.940000005</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N67" s="8">
+        <v>32216110.990000002</v>
+      </c>
+      <c r="O67">
+        <v>23320241.010000005</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>170</v>
       </c>
@@ -3860,8 +4287,14 @@
       <c r="M68" s="7">
         <v>169360507.04000002</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N68" s="8">
+        <v>249976053.09000003</v>
+      </c>
+      <c r="O68">
+        <v>206002274.16999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>171</v>
       </c>
@@ -3901,8 +4334,14 @@
       <c r="M69" s="7">
         <v>273365764.73000002</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N69" s="8">
+        <v>374521358.55999994</v>
+      </c>
+      <c r="O69">
+        <v>306950521.88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>172</v>
       </c>
@@ -3942,8 +4381,14 @@
       <c r="M70" s="7">
         <v>13878208.789999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N70" s="8">
+        <v>20506078.600000001</v>
+      </c>
+      <c r="O70">
+        <v>18587384.719999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>173</v>
       </c>
@@ -3983,8 +4428,14 @@
       <c r="M71" s="7">
         <v>20486879.740000002</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N71" s="8">
+        <v>30270878.029999994</v>
+      </c>
+      <c r="O71">
+        <v>27438520.390000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>174</v>
       </c>
@@ -4024,8 +4475,14 @@
       <c r="M72" s="7">
         <v>19826012.649999999</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N72" s="8">
+        <v>29294398.02</v>
+      </c>
+      <c r="O72">
+        <v>26553406.669999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>175</v>
       </c>
@@ -4065,8 +4522,14 @@
       <c r="M73" s="7">
         <v>20486879.740000002</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N73" s="8">
+        <v>67081657.24000001</v>
+      </c>
+      <c r="O73">
+        <v>77961948.019999996</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>176</v>
       </c>
@@ -4106,8 +4569,14 @@
       <c r="M74" s="7">
         <v>31324538.110000003</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N74" s="8">
+        <v>90842977.73999998</v>
+      </c>
+      <c r="O74">
+        <v>41050719.300000004</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>177</v>
       </c>
@@ -4147,8 +4616,14 @@
       <c r="M75" s="7">
         <v>161215582.40000001</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N75" s="8">
+        <v>274387274.58999997</v>
+      </c>
+      <c r="O75">
+        <v>289895550.25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>178</v>
       </c>
@@ -4188,8 +4663,14 @@
       <c r="M76" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N76" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O76">
+        <v>35404542.369999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>179</v>
       </c>
@@ -4229,8 +4710,14 @@
       <c r="M77" s="7">
         <v>13217341.68</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N77" s="8">
+        <v>19529598.609999999</v>
+      </c>
+      <c r="O77">
+        <v>17702271.050000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>180</v>
       </c>
@@ -4270,8 +4757,14 @@
       <c r="M78" s="7">
         <v>17182544.27</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N78" s="8">
+        <v>25388478.240000002</v>
+      </c>
+      <c r="O78">
+        <v>23012952.470000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>181</v>
       </c>
@@ -4311,8 +4804,14 @@
       <c r="M79" s="7">
         <v>23791215.239999998</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N79" s="8">
+        <v>90382781.429999992</v>
+      </c>
+      <c r="O79">
+        <v>63662073.890000008</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>182</v>
       </c>
@@ -4352,8 +4851,14 @@
       <c r="M80" s="7">
         <v>13217341.68</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N80" s="8">
+        <v>19529598.609999999</v>
+      </c>
+      <c r="O80">
+        <v>17702271.050000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>183</v>
       </c>
@@ -4393,8 +4898,14 @@
       <c r="M81" s="7">
         <v>15860810.049999999</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N81" s="8">
+        <v>39837306.809999995</v>
+      </c>
+      <c r="O81">
+        <v>40927347</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>184</v>
       </c>
@@ -4434,8 +4945,14 @@
       <c r="M82" s="7">
         <v>901698744</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N82" s="8">
+        <v>1873774774.54</v>
+      </c>
+      <c r="O82">
+        <v>1724233648.74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>185</v>
       </c>
@@ -4475,8 +4992,14 @@
       <c r="M83" s="7">
         <v>23130348.099999998</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N83" s="8">
+        <v>34176797.790000007</v>
+      </c>
+      <c r="O83">
+        <v>30978974.630000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>186</v>
       </c>
@@ -4516,8 +5039,14 @@
       <c r="M84" s="7">
         <v>49921396.739999995</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N84" s="8">
+        <v>139261554.21000001</v>
+      </c>
+      <c r="O84">
+        <v>124946725.69999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>187</v>
       </c>
@@ -4557,8 +5086,14 @@
       <c r="M85" s="7">
         <v>15199942.959999999</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N85" s="8">
+        <v>22459038.430000003</v>
+      </c>
+      <c r="O85">
+        <v>20357611.780000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>188</v>
       </c>
@@ -4598,8 +5133,14 @@
       <c r="M86" s="7">
         <v>18504278.440000001</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N86" s="8">
+        <v>27341438.229999997</v>
+      </c>
+      <c r="O86">
+        <v>24783179.660000004</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>189</v>
       </c>
@@ -4639,8 +5180,14 @@
       <c r="M87" s="7">
         <v>26434683.630000003</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N87" s="8">
+        <v>39059197.469999999</v>
+      </c>
+      <c r="O87">
+        <v>39042036.359999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>190</v>
       </c>
@@ -4680,8 +5227,14 @@
       <c r="M88" s="7">
         <v>13878208.789999999</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N88" s="8">
+        <v>20506078.600000001</v>
+      </c>
+      <c r="O88">
+        <v>18587384.719999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>191</v>
       </c>
@@ -4721,8 +5274,14 @@
       <c r="M89" s="7">
         <v>23130348.099999998</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N89" s="8">
+        <v>66245672.510000005</v>
+      </c>
+      <c r="O89">
+        <v>67996758.829999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>192</v>
       </c>
@@ -4762,8 +5321,14 @@
       <c r="M90" s="7">
         <v>22469481.07</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N90" s="8">
+        <v>33200317.870000005</v>
+      </c>
+      <c r="O90">
+        <v>30093861.040000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>193</v>
       </c>
@@ -4803,8 +5368,14 @@
       <c r="M91" s="7">
         <v>13217341.68</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N91" s="8">
+        <v>19529598.609999999</v>
+      </c>
+      <c r="O91">
+        <v>17702271.050000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>194</v>
       </c>
@@ -4844,8 +5415,14 @@
       <c r="M92" s="7">
         <v>41317403.630000003</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N92" s="8">
+        <v>44373704.560000002</v>
+      </c>
+      <c r="O92">
+        <v>33977999.420000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>195</v>
       </c>
@@ -4885,8 +5462,17 @@
       <c r="M93" s="7">
         <v>26973049.710000001</v>
       </c>
+      <c r="N93" s="8">
+        <v>44021646.330000006</v>
+      </c>
+      <c r="O93">
+        <v>41966946.299999997</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O93">
+    <sortCondition ref="B2:B93"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
